--- a/artfynd/A 49710-2025 artfynd.xlsx
+++ b/artfynd/A 49710-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129844198</v>
       </c>
       <c r="B3" t="n">
-        <v>88992</v>
+        <v>88996</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129843956</v>
       </c>
       <c r="B5" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49710-2025 artfynd.xlsx
+++ b/artfynd/A 49710-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129844198</v>
       </c>
       <c r="B3" t="n">
-        <v>88996</v>
+        <v>88998</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129843956</v>
       </c>
       <c r="B5" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>129843867</v>
       </c>
       <c r="B6" t="n">
-        <v>82916</v>
+        <v>82918</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129843927</v>
+        <v>129844264</v>
       </c>
       <c r="B8" t="n">
-        <v>82916</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1331,30 +1331,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1362,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>787351</v>
+        <v>787392</v>
       </c>
       <c r="R8" t="n">
-        <v>7116075</v>
+        <v>7116012</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1403,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>på stammen av en över 200 år gammal gran</t>
+          <t>troliga ringhack på några meters höjd i en gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,7 +1412,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129844264</v>
+        <v>129843927</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>82918</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1441,31 +1441,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1473,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>787392</v>
+        <v>787351</v>
       </c>
       <c r="R9" t="n">
-        <v>7116012</v>
+        <v>7116075</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,7 +1512,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>troliga ringhack på några meters höjd i en gran</t>
+          <t>på stammen av en över 200 år gammal gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,6 +1521,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49710-2025 artfynd.xlsx
+++ b/artfynd/A 49710-2025 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129844198</v>
+        <v>129843968</v>
       </c>
       <c r="B3" t="n">
-        <v>88998</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,27 +796,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>787399</v>
+        <v>787388</v>
       </c>
       <c r="R3" t="n">
-        <v>7115939</v>
+        <v>7116057</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,38 +890,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129843968</v>
+        <v>129843956</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>91563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>787388</v>
+        <v>787372</v>
       </c>
       <c r="R4" t="n">
-        <v>7116057</v>
+        <v>7116063</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,32 +995,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129843956</v>
+        <v>129843867</v>
       </c>
       <c r="B5" t="n">
-        <v>91563</v>
+        <v>82918</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>787372</v>
+        <v>787363</v>
       </c>
       <c r="R5" t="n">
-        <v>7116063</v>
+        <v>7116092</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,6 +1073,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på barken av en över 200 år gammal gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129843867</v>
+        <v>129843913</v>
       </c>
       <c r="B6" t="n">
-        <v>82918</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,30 +1116,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>787363</v>
+        <v>787365</v>
       </c>
       <c r="R6" t="n">
-        <v>7116092</v>
+        <v>7116087</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1188,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>på barken av en över 200 år gammal gran</t>
+          <t>hålhack i basen av en gammal gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1191,7 +1197,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129843913</v>
+        <v>129843927</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>82918</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,31 +1226,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1253,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>787365</v>
+        <v>787351</v>
       </c>
       <c r="R7" t="n">
-        <v>7116087</v>
+        <v>7116075</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,7 +1297,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>hålhack i basen av en gammal gran</t>
+          <t>på stammen av en över 200 år gammal gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,6 +1306,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1320,7 +1325,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129844264</v>
+        <v>129907975</v>
       </c>
       <c r="B8" t="n">
         <v>57736</v>
@@ -1363,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>787392</v>
+        <v>787390</v>
       </c>
       <c r="R8" t="n">
-        <v>7116012</v>
+        <v>7116008</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,17 +1398,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>troliga ringhack på några meters höjd i en gran</t>
+          <t>färska ringhack på gran, en rad med små hackmärken syns i kikaren</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129843927</v>
+        <v>129908189</v>
       </c>
       <c r="B9" t="n">
-        <v>82918</v>
+        <v>57733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1441,30 +1446,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1472,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>787351</v>
+        <v>787707</v>
       </c>
       <c r="R9" t="n">
-        <v>7116075</v>
+        <v>7115999</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,17 +1508,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>på stammen av en över 200 år gammal gran</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1527,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49710-2025 artfynd.xlsx
+++ b/artfynd/A 49710-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1543,6 +1543,116 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129844018</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hermanbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>787400</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7115944</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>hålhack i basen av en gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49710-2025 artfynd.xlsx
+++ b/artfynd/A 49710-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1653,6 +1653,116 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129923354</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hermanbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>787374</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7116052</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bygdeå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>hördes på nära håll</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49710-2025 artfynd.xlsx
+++ b/artfynd/A 49710-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844295</v>
       </c>
       <c r="B2" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129843968</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>129843956</v>
       </c>
       <c r="B4" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129843867</v>
       </c>
       <c r="B5" t="n">
-        <v>82918</v>
+        <v>82921</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129843913</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129843927</v>
       </c>
       <c r="B7" t="n">
-        <v>82918</v>
+        <v>82921</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>129907975</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>129908189</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>129844018</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129923354</v>
       </c>
       <c r="B11" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 49710-2025 artfynd.xlsx
+++ b/artfynd/A 49710-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844295</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129843968</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>129843956</v>
       </c>
       <c r="B4" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129843867</v>
       </c>
       <c r="B5" t="n">
-        <v>82921</v>
+        <v>82924</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129843913</v>
       </c>
       <c r="B6" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129843927</v>
       </c>
       <c r="B7" t="n">
-        <v>82921</v>
+        <v>82924</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>129907975</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>129908189</v>
       </c>
       <c r="B9" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>129844018</v>
       </c>
       <c r="B10" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129923354</v>
       </c>
       <c r="B11" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 49710-2025 artfynd.xlsx
+++ b/artfynd/A 49710-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129843968</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>129843956</v>
       </c>
       <c r="B4" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129843867</v>
       </c>
       <c r="B5" t="n">
-        <v>82924</v>
+        <v>82925</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129843927</v>
       </c>
       <c r="B7" t="n">
-        <v>82924</v>
+        <v>82925</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49710-2025 artfynd.xlsx
+++ b/artfynd/A 49710-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129843968</v>
       </c>
       <c r="B3" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>129843956</v>
       </c>
       <c r="B4" t="n">
-        <v>91570</v>
+        <v>91587</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129843867</v>
       </c>
       <c r="B5" t="n">
-        <v>82925</v>
+        <v>82931</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129843927</v>
       </c>
       <c r="B7" t="n">
-        <v>82925</v>
+        <v>82931</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129923354</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 49710-2025 artfynd.xlsx
+++ b/artfynd/A 49710-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129843956</v>
       </c>
       <c r="B4" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49710-2025 artfynd.xlsx
+++ b/artfynd/A 49710-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844295</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129843968</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>129843956</v>
       </c>
       <c r="B4" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129843867</v>
       </c>
       <c r="B5" t="n">
-        <v>82939</v>
+        <v>83024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129843913</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129843927</v>
       </c>
       <c r="B7" t="n">
-        <v>82939</v>
+        <v>83024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>129907975</v>
       </c>
       <c r="B8" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>129908189</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>129844018</v>
       </c>
       <c r="B10" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129923354</v>
       </c>
       <c r="B11" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 49710-2025 artfynd.xlsx
+++ b/artfynd/A 49710-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844295</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129843968</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>129843956</v>
       </c>
       <c r="B4" t="n">
-        <v>91692</v>
+        <v>91605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129843867</v>
       </c>
       <c r="B5" t="n">
-        <v>83024</v>
+        <v>82939</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129843913</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129843927</v>
       </c>
       <c r="B7" t="n">
-        <v>83024</v>
+        <v>82939</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>129907975</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>129908189</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>129844018</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129923354</v>
       </c>
       <c r="B11" t="n">
-        <v>57985</v>
+        <v>57900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 49710-2025 artfynd.xlsx
+++ b/artfynd/A 49710-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129843982</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129843867</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129843927</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129843956</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908058</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,6 +1347,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129843968</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1427,6 +1462,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129843913</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1537,6 +1577,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844018</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1647,6 +1692,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844241</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1757,6 +1807,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844295</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1867,6 +1922,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129908189</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1977,6 +2037,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129844232</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2087,6 +2152,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129907906</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2197,6 +2267,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129907975</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2307,8 +2382,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129923354</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>